--- a/GourmetProject/GameConfig/Datas/term.xlsx
+++ b/GourmetProject/GameConfig/Datas/term.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,40 +441,44 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>##type</t>
+          <t>##comment</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>术语ID</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>术语名称</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>术语解释</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr"/>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>##type</t>
+        </is>
+      </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>term_adjacent</t>
+          <t>string</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>相邻</t>
+          <t>string</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>与本菜品至少有一条公共边的其它菜品，视为与本菜品相邻。</t>
+          <t>string</t>
         </is>
       </c>
     </row>
@@ -482,17 +486,17 @@
       <c r="A4" t="inlineStr"/>
       <c r="B4" t="inlineStr">
         <is>
-          <t>term_deliciousness</t>
+          <t>term_adjacent</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>美味度</t>
+          <t>相邻</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>菜品的基础分数，在标签结算与最终汇总时参与计算。</t>
+          <t>与本菜品至少有一条公共边的其它菜品，视为与本菜品相邻。</t>
         </is>
       </c>
     </row>
@@ -500,15 +504,33 @@
       <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr">
         <is>
+          <t>term_deliciousness</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>美味度</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>菜品的基础分数，在标签结算与最终汇总时参与计算。</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr"/>
+      <c r="B6" t="inlineStr">
+        <is>
           <t>term_empty</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>空位</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>棋盘上未被任何菜品占用的格子。</t>
         </is>

--- a/GourmetProject/GameConfig/Datas/term.xlsx
+++ b/GourmetProject/GameConfig/Datas/term.xlsx
@@ -1,40 +1,446 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView windowHeight="16760"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="term" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="term" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="144525"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="20">
+  <si>
+    <t>##var</t>
+  </si>
+  <si>
+    <t>id</t>
+  </si>
+  <si>
+    <t>name</t>
+  </si>
+  <si>
+    <t>desc</t>
+  </si>
+  <si>
+    <t>##comment</t>
+  </si>
+  <si>
+    <t>术语ID</t>
+  </si>
+  <si>
+    <t>术语名称</t>
+  </si>
+  <si>
+    <t>术语解释</t>
+  </si>
+  <si>
+    <t>##type</t>
+  </si>
+  <si>
+    <t>string</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>term_adjacent</t>
+  </si>
+  <si>
+    <t>相邻</t>
+  </si>
+  <si>
+    <t>与本菜品至少有一条公共边的其它菜品，视为与本菜品相邻。</t>
+  </si>
+  <si>
+    <t>term_deliciousness</t>
+  </si>
+  <si>
+    <t>美味度</t>
+  </si>
+  <si>
+    <t>菜品的基础分数，在标签结算与最终汇总时参与计算。</t>
+  </si>
+  <si>
+    <t>term_empty</t>
+  </si>
+  <si>
+    <t>空位</t>
+  </si>
+  <si>
+    <t>棋盘上未被任何菜品占用的格子。</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="1">
-    <font>
-      <name val="Calibri"/>
-      <family val="2"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="21">
+    <font>
+      <sz val="11"/>
       <color theme="1"/>
-      <sz val="11"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
-    <fill>
-      <patternFill/>
+  <fills count="33">
+    <fill>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -42,85 +448,318 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+  <cellXfs count="3">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+  <cellStyles count="49">
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -403,140 +1042,108 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:D6"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelRow="5" outlineLevelCol="3"/>
+  <cols>
+    <col min="1" max="1" width="13.0769230769231" style="1" customWidth="1"/>
+    <col min="2" max="2" width="19.2307692307692" style="1" customWidth="1"/>
+    <col min="3" max="3" width="10.3076923076923" style="1" customWidth="1"/>
+    <col min="4" max="4" width="66.0769230769231" style="1" customWidth="1"/>
+    <col min="5" max="16384" width="9" style="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>##var</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>desc</t>
-        </is>
+    <row r="1" spans="1:4">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>##comment</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>术语ID</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>术语名称</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>术语解释</t>
-        </is>
+    <row r="2" spans="1:4">
+      <c r="A2" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>7</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>##type</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
+    <row r="3" spans="1:4">
+      <c r="A3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>9</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr"/>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>term_adjacent</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>相邻</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>与本菜品至少有一条公共边的其它菜品，视为与本菜品相邻。</t>
-        </is>
+    <row r="4" spans="1:4">
+      <c r="A4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>13</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr"/>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>term_deliciousness</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>美味度</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>菜品的基础分数，在标签结算与最终汇总时参与计算。</t>
-        </is>
+    <row r="5" spans="1:4">
+      <c r="A5" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>16</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr"/>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>term_empty</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>空位</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>棋盘上未被任何菜品占用的格子。</t>
-        </is>
+    <row r="6" spans="1:4">
+      <c r="A6" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>19</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/GourmetProject/GameConfig/Datas/term.xlsx
+++ b/GourmetProject/GameConfig/Datas/term.xlsx
@@ -1,254 +1,184 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="16760"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowHeight="16760" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="term" sheetId="1" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="term" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="144525"/>
+  <definedNames/>
+  <calcPr calcId="144525" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="20">
-  <si>
-    <t>##var</t>
-  </si>
-  <si>
-    <t>id</t>
-  </si>
-  <si>
-    <t>name</t>
-  </si>
-  <si>
-    <t>desc</t>
-  </si>
-  <si>
-    <t>##comment</t>
-  </si>
-  <si>
-    <t>术语ID</t>
-  </si>
-  <si>
-    <t>术语名称</t>
-  </si>
-  <si>
-    <t>术语解释</t>
-  </si>
-  <si>
-    <t>##type</t>
-  </si>
-  <si>
-    <t>string</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>term_adjacent</t>
-  </si>
-  <si>
-    <t>相邻</t>
-  </si>
-  <si>
-    <t>与本菜品至少有一条公共边的其它菜品，视为与本菜品相邻。</t>
-  </si>
-  <si>
-    <t>term_deliciousness</t>
-  </si>
-  <si>
-    <t>美味度</t>
-  </si>
-  <si>
-    <t>菜品的基础分数，在标签结算与最终汇总时参与计算。</t>
-  </si>
-  <si>
-    <t>term_empty</t>
-  </si>
-  <si>
-    <t>空位</t>
-  </si>
-  <si>
-    <t>棋盘上未被任何菜品占用的格子。</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
   <fonts count="21">
     <font>
-      <sz val="11"/>
+      <name val="宋体"/>
+      <charset val="134"/>
       <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="宋体"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF0000FF"/>
+      <sz val="11"/>
+      <u val="single"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF800080"/>
+      <sz val="11"/>
+      <u val="single"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FFFF0000"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="宋体"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
+      <b val="1"/>
+      <color theme="3"/>
       <sz val="18"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <i val="1"/>
+      <color rgb="FF7F7F7F"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b val="1"/>
       <color theme="3"/>
+      <sz val="15"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="宋体"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
+      <b val="1"/>
       <color theme="3"/>
+      <sz val="13"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="宋体"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
+      <b val="1"/>
       <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
       <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
       <color rgb="FF3F3F3F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
       <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
       <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
       <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
       <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
       <color rgb="FF006100"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
       <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
       <color rgb="FF9C6500"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
       <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
       <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="33">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -548,158 +478,158 @@
     </border>
   </borders>
   <cellStyleXfs count="49">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="3">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -755,11 +685,74 @@
     <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -1046,104 +1039,160 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:D6"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelRow="5" outlineLevelCol="3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D7"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8" outlineLevelRow="5"/>
   <cols>
-    <col min="1" max="1" width="13.0769230769231" style="1" customWidth="1"/>
-    <col min="2" max="2" width="19.2307692307692" style="1" customWidth="1"/>
-    <col min="3" max="3" width="10.3076923076923" style="1" customWidth="1"/>
-    <col min="4" max="4" width="66.0769230769231" style="1" customWidth="1"/>
-    <col min="5" max="16384" width="9" style="1"/>
+    <col width="13.0769230769231" customWidth="1" style="1" min="1" max="1"/>
+    <col width="19.2307692307692" customWidth="1" style="1" min="2" max="2"/>
+    <col width="10.3076923076923" customWidth="1" style="1" min="3" max="3"/>
+    <col width="66.07692307692309" customWidth="1" style="1" min="4" max="4"/>
+    <col width="9" customWidth="1" style="1" min="5" max="16384"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>##var</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>desc</t>
+        </is>
       </c>
     </row>
-    <row r="2" spans="1:4">
-      <c r="A2" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>7</v>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>##comment</t>
+        </is>
+      </c>
+      <c r="B2" s="1" t="inlineStr">
+        <is>
+          <t>术语ID</t>
+        </is>
+      </c>
+      <c r="C2" s="1" t="inlineStr">
+        <is>
+          <t>术语名称</t>
+        </is>
+      </c>
+      <c r="D2" s="1" t="inlineStr">
+        <is>
+          <t>术语解释</t>
+        </is>
       </c>
     </row>
-    <row r="3" spans="1:4">
-      <c r="A3" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>9</v>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>##type</t>
+        </is>
+      </c>
+      <c r="B3" s="1" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="C3" s="1" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="D3" s="1" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
       </c>
     </row>
-    <row r="4" spans="1:4">
-      <c r="A4" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>13</v>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr"/>
+      <c r="B4" s="1" t="inlineStr">
+        <is>
+          <t>term_adjacent</t>
+        </is>
+      </c>
+      <c r="C4" s="1" t="inlineStr">
+        <is>
+          <t>相邻</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>与本菜品至少有一条公共边的其它菜品，视为与本菜品相邻。</t>
+        </is>
       </c>
     </row>
-    <row r="5" spans="1:4">
-      <c r="A5" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>16</v>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr"/>
+      <c r="B5" s="1" t="inlineStr">
+        <is>
+          <t>term_deliciousness</t>
+        </is>
+      </c>
+      <c r="C5" s="1" t="inlineStr">
+        <is>
+          <t>美味度</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>菜品的基础分数，在标签结算与最终汇总时参与计算。</t>
+        </is>
       </c>
     </row>
-    <row r="6" spans="1:4">
-      <c r="A6" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>19</v>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr"/>
+      <c r="B6" s="1" t="inlineStr">
+        <is>
+          <t>term_empty</t>
+        </is>
+      </c>
+      <c r="C6" s="1" t="inlineStr">
+        <is>
+          <t>空位</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>棋盘上未被任何菜品占用的格子。</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr"/>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>term_sweet_transfer</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>甜蜜传递</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>使作用域内的目标食物获得本菜品的其他子技能，并在本次美食结算时随目标一并生效一次。</t>
+        </is>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
--- a/GourmetProject/GameConfig/Datas/term.xlsx
+++ b/GourmetProject/GameConfig/Datas/term.xlsx
@@ -1,184 +1,370 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowHeight="16760" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView windowHeight="15200"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="term" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="term" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="144525" fullCalcOnLoad="1"/>
+  <calcPr calcId="144525"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="56">
+  <si>
+    <t>##var</t>
+  </si>
+  <si>
+    <t>id</t>
+  </si>
+  <si>
+    <t>name</t>
+  </si>
+  <si>
+    <t>desc</t>
+  </si>
+  <si>
+    <t>##comment</t>
+  </si>
+  <si>
+    <t>术语ID</t>
+  </si>
+  <si>
+    <t>术语名称</t>
+  </si>
+  <si>
+    <t>术语解释</t>
+  </si>
+  <si>
+    <t>##type</t>
+  </si>
+  <si>
+    <t>string</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>term_sweet_transfer</t>
+  </si>
+  <si>
+    <t>甜蜜传递</t>
+  </si>
+  <si>
+    <t>使目标食物
+获得并结算此技能</t>
+  </si>
+  <si>
+    <t>t_sweet</t>
+  </si>
+  <si>
+    <t>甜</t>
+  </si>
+  <si>
+    <t>优先结算</t>
+  </si>
+  <si>
+    <t>t_bitter</t>
+  </si>
+  <si>
+    <t>苦</t>
+  </si>
+  <si>
+    <t>后置结算</t>
+  </si>
+  <si>
+    <t>t_rust</t>
+  </si>
+  <si>
+    <t>鲜</t>
+  </si>
+  <si>
+    <t>结算时
++5金币</t>
+  </si>
+  <si>
+    <t>t_numb</t>
+  </si>
+  <si>
+    <t>麻</t>
+  </si>
+  <si>
+    <t>食物旋转90度</t>
+  </si>
+  <si>
+    <t>t_sour</t>
+  </si>
+  <si>
+    <t>酸</t>
+  </si>
+  <si>
+    <t>结算时若未上菜
+场上同菜谱食物倍率 ×1.5</t>
+  </si>
+  <si>
+    <t>t_salty</t>
+  </si>
+  <si>
+    <t>咸</t>
+  </si>
+  <si>
+    <t>结算时若未上菜
+场上每有一个同菜谱食物
+ +2 金币</t>
+  </si>
+  <si>
+    <t>clb</t>
+  </si>
+  <si>
+    <t>欢乐蛋糕</t>
+  </si>
+  <si>
+    <t>根据蛋糕层数
+对场上所有蛋糕食物增益</t>
+  </si>
+  <si>
+    <t>m_cherry</t>
+  </si>
+  <si>
+    <t>樱桃木</t>
+  </si>
+  <si>
+    <t>分数+30</t>
+  </si>
+  <si>
+    <t>m_walnut</t>
+  </si>
+  <si>
+    <t>胡桃木</t>
+  </si>
+  <si>
+    <t>分数永久+10</t>
+  </si>
+  <si>
+    <t>m_marble</t>
+  </si>
+  <si>
+    <t>大理石</t>
+  </si>
+  <si>
+    <t>倍率+3</t>
+  </si>
+  <si>
+    <t>m_obsidian</t>
+  </si>
+  <si>
+    <t>黑曜石</t>
+  </si>
+  <si>
+    <t>倍率×1.5</t>
+  </si>
+  <si>
+    <t>m_emerald</t>
+  </si>
+  <si>
+    <t>翡翠</t>
+  </si>
+  <si>
+    <t>每占 1 格翡翠
+倍率+0.3</t>
+  </si>
+  <si>
+    <t>m_gold</t>
+  </si>
+  <si>
+    <t>金</t>
+  </si>
+  <si>
+    <t>占据 2 格金餐桌时
++ 10 金币</t>
+  </si>
+  <si>
+    <t>m_silver</t>
+  </si>
+  <si>
+    <t>银</t>
+  </si>
+  <si>
+    <t>占据 2 格银餐桌时
+1/3 概率获得主动道具</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
   <fonts count="21">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color theme="1"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <name val="宋体"/>
       <charset val="134"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color theme="1"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <name val="宋体"/>
       <charset val="0"/>
-      <color rgb="FF0000FF"/>
-      <sz val="11"/>
-      <u val="single"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
       <name val="宋体"/>
       <charset val="0"/>
-      <color rgb="FF800080"/>
-      <sz val="11"/>
-      <u val="single"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
       <name val="宋体"/>
       <charset val="0"/>
-      <color rgb="FFFF0000"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <b val="1"/>
-      <color theme="3"/>
-      <sz val="18"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
       <name val="宋体"/>
       <charset val="0"/>
-      <i val="1"/>
-      <color rgb="FF7F7F7F"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <b val="1"/>
-      <color theme="3"/>
-      <sz val="15"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <b val="1"/>
-      <color theme="3"/>
-      <sz val="13"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <b val="1"/>
-      <color theme="3"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
       <name val="宋体"/>
       <charset val="0"/>
-      <color rgb="FF3F3F76"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="宋体"/>
       <charset val="0"/>
-      <b val="1"/>
-      <color rgb="FF3F3F3F"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <b val="1"/>
-      <color rgb="FFFA7D00"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <b val="1"/>
-      <color rgb="FFFFFFFF"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <color rgb="FFFA7D00"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <b val="1"/>
-      <color theme="1"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <color rgb="FF006100"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <color rgb="FF9C0006"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <color rgb="FF9C6500"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <color theme="0"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="33">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -478,159 +664,168 @@
     </border>
   </borders>
   <cellStyleXfs count="49">
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+  <cellXfs count="6">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -685,74 +880,11 @@
     <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -1039,160 +1171,239 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:D7"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8" outlineLevelRow="5"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:G18"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="6"/>
   <cols>
-    <col width="13.0769230769231" customWidth="1" style="1" min="1" max="1"/>
-    <col width="19.2307692307692" customWidth="1" style="1" min="2" max="2"/>
-    <col width="10.3076923076923" customWidth="1" style="1" min="3" max="3"/>
-    <col width="66.07692307692309" customWidth="1" style="1" min="4" max="4"/>
-    <col width="9" customWidth="1" style="1" min="5" max="16384"/>
+    <col min="1" max="1" width="13.0769230769231" style="1" customWidth="1"/>
+    <col min="2" max="2" width="20.6923076923077" style="1" customWidth="1"/>
+    <col min="3" max="3" width="10.3076923076923" style="1" customWidth="1"/>
+    <col min="4" max="4" width="100" style="1" customWidth="1"/>
+    <col min="5" max="16384" width="9" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>##var</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>desc</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="1" t="inlineStr">
-        <is>
-          <t>##comment</t>
-        </is>
-      </c>
-      <c r="B2" s="1" t="inlineStr">
-        <is>
-          <t>术语ID</t>
-        </is>
-      </c>
-      <c r="C2" s="1" t="inlineStr">
-        <is>
-          <t>术语名称</t>
-        </is>
-      </c>
-      <c r="D2" s="1" t="inlineStr">
-        <is>
-          <t>术语解释</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="1" t="inlineStr">
-        <is>
-          <t>##type</t>
-        </is>
-      </c>
-      <c r="B3" s="1" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="C3" s="1" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="D3" s="1" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="inlineStr"/>
-      <c r="B4" s="1" t="inlineStr">
-        <is>
-          <t>term_adjacent</t>
-        </is>
-      </c>
-      <c r="C4" s="1" t="inlineStr">
-        <is>
-          <t>相邻</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>与本菜品至少有一条公共边的其它菜品，视为与本菜品相邻。</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="inlineStr"/>
-      <c r="B5" s="1" t="inlineStr">
-        <is>
-          <t>term_deliciousness</t>
-        </is>
-      </c>
-      <c r="C5" s="1" t="inlineStr">
-        <is>
-          <t>美味度</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>菜品的基础分数，在标签结算与最终汇总时参与计算。</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr"/>
-      <c r="B6" s="1" t="inlineStr">
-        <is>
-          <t>term_empty</t>
-        </is>
-      </c>
-      <c r="C6" s="1" t="inlineStr">
-        <is>
-          <t>空位</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>棋盘上未被任何菜品占用的格子。</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr"/>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>term_sweet_transfer</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>甜蜜传递</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>使作用域内的目标食物获得本菜品的其他子技能，并在本次美食结算时随目标一并生效一次。</t>
-        </is>
+    <row r="1" spans="1:4">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4" ht="34" spans="1:4">
+      <c r="A4" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" spans="2:4">
+      <c r="B5" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="6" spans="2:4">
+      <c r="B6" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="7" ht="34" spans="2:4">
+      <c r="B7" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="8" spans="2:4">
+      <c r="B8" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="9" ht="34" spans="2:4">
+      <c r="B9" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="10" ht="51" spans="2:4">
+      <c r="B10" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="11" ht="34" spans="2:7">
+      <c r="B11" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="E11" s="2"/>
+      <c r="F11" s="2"/>
+      <c r="G11" s="2"/>
+    </row>
+    <row r="12" spans="2:7">
+      <c r="B12" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="E12" s="2"/>
+      <c r="F12" s="2"/>
+      <c r="G12" s="2"/>
+    </row>
+    <row r="13" spans="2:7">
+      <c r="B13" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="E13" s="2"/>
+      <c r="F13" s="2"/>
+      <c r="G13" s="2"/>
+    </row>
+    <row r="14" spans="2:4">
+      <c r="B14" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="15" spans="2:4">
+      <c r="B15" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="16" ht="34" spans="2:4">
+      <c r="B16" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="D16" s="5" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="17" ht="34" spans="2:4">
+      <c r="B17" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="D17" s="5" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="18" ht="34" spans="2:4">
+      <c r="B18" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="D18" s="5" t="s">
+        <v>55</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/GourmetProject/GameConfig/Datas/term.xlsx
+++ b/GourmetProject/GameConfig/Datas/term.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="15240"/>
+    <workbookView windowHeight="15280"/>
   </bookViews>
   <sheets>
     <sheet name="term" sheetId="1" r:id="rId1"/>
@@ -84,7 +84,7 @@
   </si>
   <si>
     <t>结算时
-+5金币</t>
++8金币</t>
   </si>
   <si>
     <t>t_numb</t>
@@ -102,7 +102,7 @@
     <t>酸</t>
   </si>
   <si>
-    <t>结算开始时，若未上菜
+    <t>结算开始时，若在菜谱中
 场上食物倍率 ×1.5</t>
   </si>
   <si>
@@ -112,7 +112,7 @@
     <t>咸</t>
   </si>
   <si>
-    <t>结算开始时，若未上菜
+    <t>结算开始时，若在菜谱中
 场上食物基础分+20</t>
   </si>
   <si>
@@ -132,7 +132,7 @@
     <t>樱桃木</t>
   </si>
   <si>
-    <t>分数+30</t>
+    <t>分数+60</t>
   </si>
   <si>
     <t>m_walnut</t>
@@ -141,7 +141,7 @@
     <t>胡桃木</t>
   </si>
   <si>
-    <t>分数永久+10</t>
+    <t>分数永久+15</t>
   </si>
   <si>
     <t>m_marble</t>
@@ -150,7 +150,7 @@
     <t>大理石</t>
   </si>
   <si>
-    <t>倍率+3</t>
+    <t>倍率+2</t>
   </si>
   <si>
     <t>m_obsidian</t>
@@ -169,7 +169,7 @@
   </si>
   <si>
     <t>每占 1 格翡翠
-倍率+0.3</t>
+倍率+0.8</t>
   </si>
   <si>
     <t>m_gold</t>
@@ -179,7 +179,7 @@
   </si>
   <si>
     <t>占据 2 格金餐桌时
-+ 10 金币</t>
++ 15 金币</t>
   </si>
   <si>
     <t>m_silver</t>
@@ -189,7 +189,7 @@
   </si>
   <si>
     <t>占据 2 格银餐桌时
-1/3 概率获得主动道具</t>
+1/2概率获得主动道具</t>
   </si>
 </sst>
 </file>

--- a/GourmetProject/GameConfig/Datas/term.xlsx
+++ b/GourmetProject/GameConfig/Datas/term.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="term" sheetId="1" r:id="R01c9d7a54f364ef7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="term" sheetId="1" r:id="Rf685490a672247b3"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -77,10 +77,6 @@
     <x:t xml:space="preserve">鲜</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">结算时
-+8金币</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">t_numb</x:t>
   </x:si>
   <x:si>
@@ -96,18 +92,10 @@
     <x:t xml:space="preserve">酸</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">结算开始时，若在菜谱中
-场上食物倍率 ×1.5</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">t_salty</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">咸</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">结算开始时，若在菜谱中
-场上食物基础分+20</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">clb</x:t>
@@ -126,44 +114,28 @@
     <x:t xml:space="preserve">樱桃木</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">分数+60</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">m_walnut</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">胡桃木</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">分数永久+15</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">m_marble</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">大理石</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">倍率+2</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">m_obsidian</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">黑曜石</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">倍率×1.5</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">m_emerald</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">翡翠</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">每占 1 格翡翠
-倍率+0.8</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">m_gold</x:t>
@@ -180,10 +152,6 @@
   </x:si>
   <x:si>
     <x:t xml:space="preserve">银</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">占据 2 格银餐桌时
-1/2概率获得主动道具</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -1251,129 +1219,134 @@
       <x:c r="C7" s="1" t="s">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="D7" s="2" t="s">
-        <x:v>22</x:v>
+      <x:c r="D7" s="2" t="str">
+        <x:v>结算时
++8 金币</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
       <x:c r="B8" s="1" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="C8" s="1" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="C8" s="1" t="s">
+      <x:c r="D8" s="1" t="s">
         <x:v>24</x:v>
-      </x:c>
-      <x:c r="D8" s="1" t="s">
-        <x:v>25</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="34">
       <x:c r="B9" s="1" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="C9" s="1" t="s">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="C9" s="1" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="D9" s="2" t="s">
-        <x:v>28</x:v>
+      <x:c r="D9" s="2" t="str">
+        <x:v>结算开始时，若在食谱中
+场上食物倍率 ×1.5</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="34">
       <x:c r="B10" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C10" s="1" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="D10" s="2" t="s">
-        <x:v>31</x:v>
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="D10" s="2" t="str">
+        <x:v>结算开始时，若在食谱中
+场上食物基础分数 +20</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="34">
       <x:c r="B11" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C11" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="D11" s="2" t="s">
-        <x:v>34</x:v>
+        <x:v>31</x:v>
       </x:c>
     </x:row>
     <x:row r="12">
       <x:c r="B12" s="3" t="s">
-        <x:v>35</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C12" s="3" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="D12" s="3" t="s">
-        <x:v>37</x:v>
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="D12" s="3" t="str">
+        <x:v>分数 +60</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
       <x:c r="B13" s="3" t="s">
-        <x:v>38</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C13" s="3" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="D13" s="3" t="s">
-        <x:v>40</x:v>
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="D13" s="3" t="str">
+        <x:v>分数永久 +15</x:v>
       </x:c>
     </x:row>
     <x:row r="14">
       <x:c r="B14" s="3" t="s">
-        <x:v>41</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C14" s="3" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="D14" s="3" t="s">
-        <x:v>43</x:v>
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="D14" s="3" t="str">
+        <x:v>倍率 +2</x:v>
       </x:c>
     </x:row>
     <x:row r="15">
       <x:c r="B15" s="3" t="s">
-        <x:v>44</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C15" s="3" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="D15" s="3" t="s">
-        <x:v>46</x:v>
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="D15" s="3" t="str">
+        <x:v>倍率 ×1.5</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="34">
       <x:c r="B16" s="3" t="s">
-        <x:v>47</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C16" s="3" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="D16" s="4" t="s">
-        <x:v>49</x:v>
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="D16" s="4" t="str">
+        <x:v>每占 1 格翡翠
+倍率 +0.8</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="34">
       <x:c r="B17" s="3" t="s">
-        <x:v>50</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="C17" s="3" t="s">
-        <x:v>51</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="D17" s="4" t="s">
-        <x:v>52</x:v>
+        <x:v>44</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="34">
       <x:c r="B18" s="3" t="s">
-        <x:v>53</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="C18" s="3" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="D18" s="4" t="s">
-        <x:v>55</x:v>
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="D18" s="4" t="str">
+        <x:v>占据 2 格银餐桌时
+1/2概率获得消耗品</x:v>
       </x:c>
     </x:row>
     <x:row r="19">

--- a/GourmetProject/GameConfig/Datas/term.xlsx
+++ b/GourmetProject/GameConfig/Datas/term.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="term" sheetId="1" r:id="Rf685490a672247b3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="term" sheetId="1" r:id="Rf36ea7b4d5834882"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -142,10 +142,6 @@
   </x:si>
   <x:si>
     <x:t xml:space="preserve">金</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">占据 2 格金餐桌时
-+ 15 金币</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">m_silver</x:t>
@@ -1221,7 +1217,7 @@
       </x:c>
       <x:c r="D7" s="2" t="str">
         <x:v>结算时
-+8 金币</x:v>
++10 金币</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
@@ -1333,20 +1329,21 @@
       <x:c r="C17" s="3" t="s">
         <x:v>43</x:v>
       </x:c>
-      <x:c r="D17" s="4" t="s">
-        <x:v>44</x:v>
+      <x:c r="D17" s="4" t="str">
+        <x:v>占据 2 格金餐桌时
++15 金币</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="34">
       <x:c r="B18" s="3" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="C18" s="3" t="s">
         <x:v>45</x:v>
-      </x:c>
-      <x:c r="C18" s="3" t="s">
-        <x:v>46</x:v>
       </x:c>
       <x:c r="D18" s="4" t="str">
         <x:v>占据 2 格银餐桌时
-1/2概率获得消耗品</x:v>
+1/2 概率获得消耗品</x:v>
       </x:c>
     </x:row>
     <x:row r="19">

--- a/GourmetProject/GameConfig/Datas/term.xlsx
+++ b/GourmetProject/GameConfig/Datas/term.xlsx
@@ -2,154 +2,13 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="term" sheetId="1" r:id="Rf36ea7b4d5834882"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="term" sheetId="1" r:id="Rc6ab822897d54a10"/>
   </x:sheets>
 </x:workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:si>
-    <x:t xml:space="preserve">##var</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">id</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">name</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">desc</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">##comment</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">术语ID</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">术语名称</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">术语解释</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">##type</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">string</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">10</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">term_sweet_transfer</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">甜蜜传递</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">使随机食物
-获得并结算此技能</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">t_sweet</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">甜</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">优先结算</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">t_bitter</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">苦</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">后置结算</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">t_rust</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">鲜</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">t_numb</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">麻</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">食物旋转90度</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">t_sour</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">酸</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">t_salty</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">咸</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">clb</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">欢乐蛋糕</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">根据蛋糕层数
-对场上所有蛋糕食物增益</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">m_cherry</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">樱桃木</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">m_walnut</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">胡桃木</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">m_marble</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">大理石</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">m_obsidian</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">黑曜石</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">m_emerald</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">翡翠</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">m_gold</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">金</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">m_silver</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">银</x:t>
-  </x:si>
-</x:sst>
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1131,220 +990,270 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1">
-      <x:c r="A1" s="1" t="s">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="B1" s="1" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C1" s="1" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D1" s="1" t="s">
-        <x:v>3</x:v>
-      </x:c>
+      <x:c r="A1" s="1" t="str">
+        <x:v>##var</x:v>
+      </x:c>
+      <x:c r="B1" s="1" t="str">
+        <x:v>id</x:v>
+      </x:c>
+      <x:c r="C1" s="1" t="str">
+        <x:v>name</x:v>
+      </x:c>
+      <x:c r="D1" s="1" t="str">
+        <x:v>desc</x:v>
+      </x:c>
+      <x:c r="E1"/>
+      <x:c r="F1"/>
     </x:row>
     <x:row r="2">
-      <x:c r="A2" s="1" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="B2" s="1" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C2" s="1" t="s">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="D2" s="1" t="s">
-        <x:v>7</x:v>
-      </x:c>
+      <x:c r="A2" s="1" t="str">
+        <x:v>##comment</x:v>
+      </x:c>
+      <x:c r="B2" s="1" t="str">
+        <x:v>术语ID</x:v>
+      </x:c>
+      <x:c r="C2" s="1" t="str">
+        <x:v>术语名称</x:v>
+      </x:c>
+      <x:c r="D2" s="1" t="str">
+        <x:v>术语解释</x:v>
+      </x:c>
+      <x:c r="E2"/>
+      <x:c r="F2"/>
     </x:row>
     <x:row r="3">
-      <x:c r="A3" s="1" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="B3" s="1" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="C3" s="1" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="D3" s="1" t="s">
-        <x:v>9</x:v>
-      </x:c>
+      <x:c r="A3" s="1" t="str">
+        <x:v>##type</x:v>
+      </x:c>
+      <x:c r="B3" s="1" t="str">
+        <x:v>string</x:v>
+      </x:c>
+      <x:c r="C3" s="1" t="str">
+        <x:v>string</x:v>
+      </x:c>
+      <x:c r="D3" s="1" t="str">
+        <x:v>string</x:v>
+      </x:c>
+      <x:c r="E3"/>
+      <x:c r="F3"/>
     </x:row>
     <x:row r="4" ht="34">
-      <x:c r="A4" s="1" t="s">
+      <x:c r="A4" s="1" t="str">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="B4" s="1" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="C4" s="1" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="D4" s="2" t="s">
-        <x:v>13</x:v>
-      </x:c>
+      <x:c r="B4" s="1" t="str">
+        <x:v>term_sweet_transfer</x:v>
+      </x:c>
+      <x:c r="C4" s="1" t="str">
+        <x:v>甜蜜传递</x:v>
+      </x:c>
+      <x:c r="D4" s="2" t="str">
+        <x:v>使随机食物
+获得并结算此技能</x:v>
+      </x:c>
+      <x:c r="E4"/>
+      <x:c r="F4"/>
     </x:row>
     <x:row r="5">
-      <x:c r="B5" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C5" s="1" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="D5" s="1" t="s">
-        <x:v>16</x:v>
-      </x:c>
+      <x:c r="A5"/>
+      <x:c r="B5" s="1" t="str">
+        <x:v>t_sweet</x:v>
+      </x:c>
+      <x:c r="C5" s="1" t="str">
+        <x:v>甜</x:v>
+      </x:c>
+      <x:c r="D5" s="1" t="str">
+        <x:v>优先结算</x:v>
+      </x:c>
+      <x:c r="E5"/>
+      <x:c r="F5"/>
     </x:row>
     <x:row r="6">
-      <x:c r="B6" s="1" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="C6" s="1" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="D6" s="1" t="s">
-        <x:v>19</x:v>
-      </x:c>
+      <x:c r="A6"/>
+      <x:c r="B6" s="1" t="str">
+        <x:v>t_bitter</x:v>
+      </x:c>
+      <x:c r="C6" s="1" t="str">
+        <x:v>苦</x:v>
+      </x:c>
+      <x:c r="D6" s="1" t="str">
+        <x:v>后置结算</x:v>
+      </x:c>
+      <x:c r="E6"/>
+      <x:c r="F6"/>
     </x:row>
     <x:row r="7" ht="34">
-      <x:c r="B7" s="1" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="C7" s="1" t="s">
-        <x:v>21</x:v>
+      <x:c r="A7"/>
+      <x:c r="B7" s="1" t="str">
+        <x:v>t_fresh</x:v>
+      </x:c>
+      <x:c r="C7" s="1" t="str">
+        <x:v>鲜</x:v>
       </x:c>
       <x:c r="D7" s="2" t="str">
-        <x:v>结算时
-+10 金币</x:v>
-      </x:c>
+        <x:v>优先出菜</x:v>
+      </x:c>
+      <x:c r="E7"/>
+      <x:c r="F7"/>
     </x:row>
     <x:row r="8">
-      <x:c r="B8" s="1" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="C8" s="1" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="D8" s="1" t="s">
-        <x:v>24</x:v>
-      </x:c>
+      <x:c r="A8"/>
+      <x:c r="B8" s="1" t="str">
+        <x:v>t_numb</x:v>
+      </x:c>
+      <x:c r="C8" s="1" t="str">
+        <x:v>麻</x:v>
+      </x:c>
+      <x:c r="D8" s="1" t="str">
+        <x:v>食物旋转90度</x:v>
+      </x:c>
+      <x:c r="E8"/>
+      <x:c r="F8"/>
     </x:row>
     <x:row r="9" ht="34">
-      <x:c r="B9" s="1" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="C9" s="1" t="s">
-        <x:v>26</x:v>
+      <x:c r="A9"/>
+      <x:c r="B9" s="1" t="str">
+        <x:v>t_sour</x:v>
+      </x:c>
+      <x:c r="C9" s="1" t="str">
+        <x:v>酸</x:v>
       </x:c>
       <x:c r="D9" s="2" t="str">
-        <x:v>结算开始时，若在食谱中
-场上食物倍率 ×1.5</x:v>
-      </x:c>
+        <x:v>结算开始时，若仍在食谱中
+场上食物倍率 +0.5</x:v>
+      </x:c>
+      <x:c r="E9"/>
+      <x:c r="F9"/>
     </x:row>
     <x:row r="10" ht="34">
-      <x:c r="B10" s="1" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="C10" s="1" t="s">
-        <x:v>28</x:v>
+      <x:c r="A10"/>
+      <x:c r="B10" s="1" t="str">
+        <x:v>t_salty</x:v>
+      </x:c>
+      <x:c r="C10" s="1" t="str">
+        <x:v>咸</x:v>
       </x:c>
       <x:c r="D10" s="2" t="str">
-        <x:v>结算开始时，若在食谱中
-场上食物基础分数 +20</x:v>
-      </x:c>
+        <x:v>有 20% 概率额外结算 1 次</x:v>
+      </x:c>
+      <x:c r="E10"/>
+      <x:c r="F10"/>
     </x:row>
     <x:row r="11" ht="34">
-      <x:c r="B11" s="1" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="C11" s="1" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="D11" s="2" t="s">
-        <x:v>31</x:v>
-      </x:c>
+      <x:c r="A11"/>
+      <x:c r="B11" s="1" t="str">
+        <x:v>clb</x:v>
+      </x:c>
+      <x:c r="C11" s="1" t="str">
+        <x:v>欢乐蛋糕</x:v>
+      </x:c>
+      <x:c r="D11" s="2" t="str">
+        <x:v>根据蛋糕层数
+对场上所有蛋糕食物增益</x:v>
+      </x:c>
+      <x:c r="E11"/>
+      <x:c r="F11"/>
     </x:row>
     <x:row r="12">
-      <x:c r="B12" s="3" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="C12" s="3" t="s">
-        <x:v>33</x:v>
+      <x:c r="A12"/>
+      <x:c r="B12" s="3" t="str">
+        <x:v>m_cherry</x:v>
+      </x:c>
+      <x:c r="C12" s="3" t="str">
+        <x:v>樱桃木</x:v>
       </x:c>
       <x:c r="D12" s="3" t="str">
         <x:v>分数 +60</x:v>
       </x:c>
+      <x:c r="E12"/>
+      <x:c r="F12"/>
     </x:row>
     <x:row r="13">
-      <x:c r="B13" s="3" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="C13" s="3" t="s">
-        <x:v>35</x:v>
+      <x:c r="A13"/>
+      <x:c r="B13" s="3" t="str">
+        <x:v>m_walnut</x:v>
+      </x:c>
+      <x:c r="C13" s="3" t="str">
+        <x:v>胡桃木</x:v>
       </x:c>
       <x:c r="D13" s="3" t="str">
         <x:v>分数永久 +15</x:v>
       </x:c>
+      <x:c r="E13"/>
+      <x:c r="F13"/>
     </x:row>
     <x:row r="14">
-      <x:c r="B14" s="3" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="C14" s="3" t="s">
-        <x:v>37</x:v>
+      <x:c r="A14"/>
+      <x:c r="B14" s="3" t="str">
+        <x:v>m_marble</x:v>
+      </x:c>
+      <x:c r="C14" s="3" t="str">
+        <x:v>大理石</x:v>
       </x:c>
       <x:c r="D14" s="3" t="str">
         <x:v>倍率 +2</x:v>
       </x:c>
+      <x:c r="E14"/>
+      <x:c r="F14"/>
     </x:row>
     <x:row r="15">
-      <x:c r="B15" s="3" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="C15" s="3" t="s">
-        <x:v>39</x:v>
+      <x:c r="A15"/>
+      <x:c r="B15" s="3" t="str">
+        <x:v>m_obsidian</x:v>
+      </x:c>
+      <x:c r="C15" s="3" t="str">
+        <x:v>黑曜石</x:v>
       </x:c>
       <x:c r="D15" s="3" t="str">
         <x:v>倍率 ×1.5</x:v>
       </x:c>
+      <x:c r="E15"/>
+      <x:c r="F15"/>
     </x:row>
     <x:row r="16" ht="34">
-      <x:c r="B16" s="3" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="C16" s="3" t="s">
-        <x:v>41</x:v>
+      <x:c r="A16"/>
+      <x:c r="B16" s="3" t="str">
+        <x:v>m_emerald</x:v>
+      </x:c>
+      <x:c r="C16" s="3" t="str">
+        <x:v>翡翠</x:v>
       </x:c>
       <x:c r="D16" s="4" t="str">
         <x:v>每占 1 格翡翠
 倍率 +0.8</x:v>
       </x:c>
+      <x:c r="E16"/>
+      <x:c r="F16"/>
     </x:row>
     <x:row r="17" ht="34">
-      <x:c r="B17" s="3" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="C17" s="3" t="s">
-        <x:v>43</x:v>
+      <x:c r="A17"/>
+      <x:c r="B17" s="3" t="str">
+        <x:v>m_gold</x:v>
+      </x:c>
+      <x:c r="C17" s="3" t="str">
+        <x:v>金</x:v>
       </x:c>
       <x:c r="D17" s="4" t="str">
         <x:v>占据 2 格金餐桌时
 +15 金币</x:v>
       </x:c>
+      <x:c r="E17"/>
+      <x:c r="F17"/>
     </x:row>
     <x:row r="18" ht="34">
-      <x:c r="B18" s="3" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="C18" s="3" t="s">
-        <x:v>45</x:v>
+      <x:c r="A18"/>
+      <x:c r="B18" s="3" t="str">
+        <x:v>m_silver</x:v>
+      </x:c>
+      <x:c r="C18" s="3" t="str">
+        <x:v>银</x:v>
       </x:c>
       <x:c r="D18" s="4" t="str">
         <x:v>占据 2 格银餐桌时
 1/2 概率获得消耗品</x:v>
       </x:c>
+      <x:c r="E18"/>
+      <x:c r="F18"/>
     </x:row>
     <x:row r="19">
       <x:c r="A19"/>
@@ -1357,6 +1266,1456 @@
       <x:c r="D19" t="str">
         <x:v>视为{x}个食物</x:v>
       </x:c>
+      <x:c r="E19"/>
+      <x:c r="F19"/>
+    </x:row>
+    <x:row r="20">
+      <x:c r="A20"/>
+      <x:c r="B20"/>
+      <x:c r="C20"/>
+      <x:c r="D20"/>
+      <x:c r="E20"/>
+      <x:c r="F20"/>
+    </x:row>
+    <x:row r="21">
+      <x:c r="A21"/>
+      <x:c r="B21"/>
+      <x:c r="C21"/>
+      <x:c r="D21"/>
+      <x:c r="E21"/>
+      <x:c r="F21"/>
+    </x:row>
+    <x:row r="22">
+      <x:c r="A22"/>
+      <x:c r="B22"/>
+      <x:c r="C22"/>
+      <x:c r="D22"/>
+      <x:c r="E22"/>
+      <x:c r="F22"/>
+    </x:row>
+    <x:row r="23">
+      <x:c r="A23"/>
+      <x:c r="B23"/>
+      <x:c r="C23"/>
+      <x:c r="D23"/>
+      <x:c r="E23"/>
+      <x:c r="F23"/>
+    </x:row>
+    <x:row r="24">
+      <x:c r="A24"/>
+      <x:c r="B24"/>
+      <x:c r="C24"/>
+      <x:c r="D24"/>
+      <x:c r="E24"/>
+      <x:c r="F24"/>
+    </x:row>
+    <x:row r="25">
+      <x:c r="A25"/>
+      <x:c r="B25"/>
+      <x:c r="C25"/>
+      <x:c r="D25"/>
+      <x:c r="E25"/>
+      <x:c r="F25"/>
+    </x:row>
+    <x:row r="26">
+      <x:c r="A26"/>
+      <x:c r="B26"/>
+      <x:c r="C26"/>
+      <x:c r="D26"/>
+      <x:c r="E26"/>
+      <x:c r="F26"/>
+    </x:row>
+    <x:row r="27">
+      <x:c r="A27"/>
+      <x:c r="B27"/>
+      <x:c r="C27"/>
+      <x:c r="D27"/>
+      <x:c r="E27"/>
+      <x:c r="F27"/>
+    </x:row>
+    <x:row r="28">
+      <x:c r="A28"/>
+      <x:c r="B28"/>
+      <x:c r="C28"/>
+      <x:c r="D28"/>
+      <x:c r="E28"/>
+      <x:c r="F28"/>
+    </x:row>
+    <x:row r="29">
+      <x:c r="A29"/>
+      <x:c r="B29"/>
+      <x:c r="C29"/>
+      <x:c r="D29"/>
+      <x:c r="E29"/>
+      <x:c r="F29"/>
+    </x:row>
+    <x:row r="30">
+      <x:c r="A30"/>
+      <x:c r="B30"/>
+      <x:c r="C30"/>
+      <x:c r="D30"/>
+      <x:c r="E30"/>
+      <x:c r="F30"/>
+    </x:row>
+    <x:row r="31">
+      <x:c r="A31"/>
+      <x:c r="B31"/>
+      <x:c r="C31"/>
+      <x:c r="D31"/>
+      <x:c r="E31"/>
+      <x:c r="F31"/>
+    </x:row>
+    <x:row r="32">
+      <x:c r="A32"/>
+      <x:c r="B32"/>
+      <x:c r="C32"/>
+      <x:c r="D32"/>
+      <x:c r="E32"/>
+      <x:c r="F32"/>
+    </x:row>
+    <x:row r="33">
+      <x:c r="A33"/>
+      <x:c r="B33"/>
+      <x:c r="C33"/>
+      <x:c r="D33"/>
+      <x:c r="E33"/>
+      <x:c r="F33"/>
+    </x:row>
+    <x:row r="34">
+      <x:c r="A34"/>
+      <x:c r="B34"/>
+      <x:c r="C34"/>
+      <x:c r="D34"/>
+      <x:c r="E34"/>
+      <x:c r="F34"/>
+    </x:row>
+    <x:row r="35">
+      <x:c r="A35"/>
+      <x:c r="B35"/>
+      <x:c r="C35"/>
+      <x:c r="D35"/>
+      <x:c r="E35"/>
+      <x:c r="F35"/>
+    </x:row>
+    <x:row r="36">
+      <x:c r="A36"/>
+      <x:c r="B36"/>
+      <x:c r="C36"/>
+      <x:c r="D36"/>
+      <x:c r="E36"/>
+      <x:c r="F36"/>
+    </x:row>
+    <x:row r="37">
+      <x:c r="A37"/>
+      <x:c r="B37"/>
+      <x:c r="C37"/>
+      <x:c r="D37"/>
+      <x:c r="E37"/>
+      <x:c r="F37"/>
+    </x:row>
+    <x:row r="38">
+      <x:c r="A38"/>
+      <x:c r="B38"/>
+      <x:c r="C38"/>
+      <x:c r="D38"/>
+      <x:c r="E38"/>
+      <x:c r="F38"/>
+    </x:row>
+    <x:row r="39">
+      <x:c r="A39"/>
+      <x:c r="B39"/>
+      <x:c r="C39"/>
+      <x:c r="D39"/>
+      <x:c r="E39"/>
+      <x:c r="F39"/>
+    </x:row>
+    <x:row r="40">
+      <x:c r="A40"/>
+      <x:c r="B40"/>
+      <x:c r="C40"/>
+      <x:c r="D40"/>
+      <x:c r="E40"/>
+      <x:c r="F40"/>
+    </x:row>
+    <x:row r="41">
+      <x:c r="A41"/>
+      <x:c r="B41"/>
+      <x:c r="C41"/>
+      <x:c r="D41"/>
+      <x:c r="E41"/>
+      <x:c r="F41"/>
+    </x:row>
+    <x:row r="42">
+      <x:c r="A42"/>
+      <x:c r="B42"/>
+      <x:c r="C42"/>
+      <x:c r="D42"/>
+      <x:c r="E42"/>
+      <x:c r="F42"/>
+    </x:row>
+    <x:row r="43">
+      <x:c r="A43"/>
+      <x:c r="B43"/>
+      <x:c r="C43"/>
+      <x:c r="D43"/>
+      <x:c r="E43"/>
+      <x:c r="F43"/>
+    </x:row>
+    <x:row r="44">
+      <x:c r="A44"/>
+      <x:c r="B44"/>
+      <x:c r="C44"/>
+      <x:c r="D44"/>
+      <x:c r="E44"/>
+      <x:c r="F44"/>
+    </x:row>
+    <x:row r="45">
+      <x:c r="A45"/>
+      <x:c r="B45"/>
+      <x:c r="C45"/>
+      <x:c r="D45"/>
+      <x:c r="E45"/>
+      <x:c r="F45"/>
+    </x:row>
+    <x:row r="46">
+      <x:c r="A46"/>
+      <x:c r="B46"/>
+      <x:c r="C46"/>
+      <x:c r="D46"/>
+      <x:c r="E46"/>
+      <x:c r="F46"/>
+    </x:row>
+    <x:row r="47">
+      <x:c r="A47"/>
+      <x:c r="B47"/>
+      <x:c r="C47"/>
+      <x:c r="D47"/>
+      <x:c r="E47"/>
+      <x:c r="F47"/>
+    </x:row>
+    <x:row r="48">
+      <x:c r="A48"/>
+      <x:c r="B48"/>
+      <x:c r="C48"/>
+      <x:c r="D48"/>
+      <x:c r="E48"/>
+      <x:c r="F48"/>
+    </x:row>
+    <x:row r="49">
+      <x:c r="A49"/>
+      <x:c r="B49"/>
+      <x:c r="C49"/>
+      <x:c r="D49"/>
+      <x:c r="E49"/>
+      <x:c r="F49"/>
+    </x:row>
+    <x:row r="50">
+      <x:c r="A50"/>
+      <x:c r="B50"/>
+      <x:c r="C50"/>
+      <x:c r="D50"/>
+      <x:c r="E50"/>
+      <x:c r="F50"/>
+    </x:row>
+    <x:row r="51">
+      <x:c r="A51"/>
+      <x:c r="B51"/>
+      <x:c r="C51"/>
+      <x:c r="D51"/>
+      <x:c r="E51"/>
+      <x:c r="F51"/>
+    </x:row>
+    <x:row r="52">
+      <x:c r="A52"/>
+      <x:c r="B52"/>
+      <x:c r="C52"/>
+      <x:c r="D52"/>
+      <x:c r="E52"/>
+      <x:c r="F52"/>
+    </x:row>
+    <x:row r="53">
+      <x:c r="A53"/>
+      <x:c r="B53"/>
+      <x:c r="C53"/>
+      <x:c r="D53"/>
+      <x:c r="E53"/>
+      <x:c r="F53"/>
+    </x:row>
+    <x:row r="54">
+      <x:c r="A54"/>
+      <x:c r="B54"/>
+      <x:c r="C54"/>
+      <x:c r="D54"/>
+      <x:c r="E54"/>
+      <x:c r="F54"/>
+    </x:row>
+    <x:row r="55">
+      <x:c r="A55"/>
+      <x:c r="B55"/>
+      <x:c r="C55"/>
+      <x:c r="D55"/>
+      <x:c r="E55"/>
+      <x:c r="F55"/>
+    </x:row>
+    <x:row r="56">
+      <x:c r="A56"/>
+      <x:c r="B56"/>
+      <x:c r="C56"/>
+      <x:c r="D56"/>
+      <x:c r="E56"/>
+      <x:c r="F56"/>
+    </x:row>
+    <x:row r="57">
+      <x:c r="A57"/>
+      <x:c r="B57"/>
+      <x:c r="C57"/>
+      <x:c r="D57"/>
+      <x:c r="E57"/>
+      <x:c r="F57"/>
+    </x:row>
+    <x:row r="58">
+      <x:c r="A58"/>
+      <x:c r="B58"/>
+      <x:c r="C58"/>
+      <x:c r="D58"/>
+      <x:c r="E58"/>
+      <x:c r="F58"/>
+    </x:row>
+    <x:row r="59">
+      <x:c r="A59"/>
+      <x:c r="B59"/>
+      <x:c r="C59"/>
+      <x:c r="D59"/>
+      <x:c r="E59"/>
+      <x:c r="F59"/>
+    </x:row>
+    <x:row r="60">
+      <x:c r="A60"/>
+      <x:c r="B60"/>
+      <x:c r="C60"/>
+      <x:c r="D60"/>
+      <x:c r="E60"/>
+      <x:c r="F60"/>
+    </x:row>
+    <x:row r="61">
+      <x:c r="A61"/>
+      <x:c r="B61"/>
+      <x:c r="C61"/>
+      <x:c r="D61"/>
+      <x:c r="E61"/>
+      <x:c r="F61"/>
+    </x:row>
+    <x:row r="62">
+      <x:c r="A62"/>
+      <x:c r="B62"/>
+      <x:c r="C62"/>
+      <x:c r="D62"/>
+      <x:c r="E62"/>
+      <x:c r="F62"/>
+    </x:row>
+    <x:row r="63">
+      <x:c r="A63"/>
+      <x:c r="B63"/>
+      <x:c r="C63"/>
+      <x:c r="D63"/>
+      <x:c r="E63"/>
+      <x:c r="F63"/>
+    </x:row>
+    <x:row r="64">
+      <x:c r="A64"/>
+      <x:c r="B64"/>
+      <x:c r="C64"/>
+      <x:c r="D64"/>
+      <x:c r="E64"/>
+      <x:c r="F64"/>
+    </x:row>
+    <x:row r="65">
+      <x:c r="A65"/>
+      <x:c r="B65"/>
+      <x:c r="C65"/>
+      <x:c r="D65"/>
+      <x:c r="E65"/>
+      <x:c r="F65"/>
+    </x:row>
+    <x:row r="66">
+      <x:c r="A66"/>
+      <x:c r="B66"/>
+      <x:c r="C66"/>
+      <x:c r="D66"/>
+      <x:c r="E66"/>
+      <x:c r="F66"/>
+    </x:row>
+    <x:row r="67">
+      <x:c r="A67"/>
+      <x:c r="B67"/>
+      <x:c r="C67"/>
+      <x:c r="D67"/>
+      <x:c r="E67"/>
+      <x:c r="F67"/>
+    </x:row>
+    <x:row r="68">
+      <x:c r="A68"/>
+      <x:c r="B68"/>
+      <x:c r="C68"/>
+      <x:c r="D68"/>
+      <x:c r="E68"/>
+      <x:c r="F68"/>
+    </x:row>
+    <x:row r="69">
+      <x:c r="A69"/>
+      <x:c r="B69"/>
+      <x:c r="C69"/>
+      <x:c r="D69"/>
+      <x:c r="E69"/>
+      <x:c r="F69"/>
+    </x:row>
+    <x:row r="70">
+      <x:c r="A70"/>
+      <x:c r="B70"/>
+      <x:c r="C70"/>
+      <x:c r="D70"/>
+      <x:c r="E70"/>
+      <x:c r="F70"/>
+    </x:row>
+    <x:row r="71">
+      <x:c r="A71"/>
+      <x:c r="B71"/>
+      <x:c r="C71"/>
+      <x:c r="D71"/>
+      <x:c r="E71"/>
+      <x:c r="F71"/>
+    </x:row>
+    <x:row r="72">
+      <x:c r="A72"/>
+      <x:c r="B72"/>
+      <x:c r="C72"/>
+      <x:c r="D72"/>
+      <x:c r="E72"/>
+      <x:c r="F72"/>
+    </x:row>
+    <x:row r="73">
+      <x:c r="A73"/>
+      <x:c r="B73"/>
+      <x:c r="C73"/>
+      <x:c r="D73"/>
+      <x:c r="E73"/>
+      <x:c r="F73"/>
+    </x:row>
+    <x:row r="74">
+      <x:c r="A74"/>
+      <x:c r="B74"/>
+      <x:c r="C74"/>
+      <x:c r="D74"/>
+      <x:c r="E74"/>
+      <x:c r="F74"/>
+    </x:row>
+    <x:row r="75">
+      <x:c r="A75"/>
+      <x:c r="B75"/>
+      <x:c r="C75"/>
+      <x:c r="D75"/>
+      <x:c r="E75"/>
+      <x:c r="F75"/>
+    </x:row>
+    <x:row r="76">
+      <x:c r="A76"/>
+      <x:c r="B76"/>
+      <x:c r="C76"/>
+      <x:c r="D76"/>
+      <x:c r="E76"/>
+      <x:c r="F76"/>
+    </x:row>
+    <x:row r="77">
+      <x:c r="A77"/>
+      <x:c r="B77"/>
+      <x:c r="C77"/>
+      <x:c r="D77"/>
+      <x:c r="E77"/>
+      <x:c r="F77"/>
+    </x:row>
+    <x:row r="78">
+      <x:c r="A78"/>
+      <x:c r="B78"/>
+      <x:c r="C78"/>
+      <x:c r="D78"/>
+      <x:c r="E78"/>
+      <x:c r="F78"/>
+    </x:row>
+    <x:row r="79">
+      <x:c r="A79"/>
+      <x:c r="B79"/>
+      <x:c r="C79"/>
+      <x:c r="D79"/>
+      <x:c r="E79"/>
+      <x:c r="F79"/>
+    </x:row>
+    <x:row r="80">
+      <x:c r="A80"/>
+      <x:c r="B80"/>
+      <x:c r="C80"/>
+      <x:c r="D80"/>
+      <x:c r="E80"/>
+      <x:c r="F80"/>
+    </x:row>
+    <x:row r="81">
+      <x:c r="A81"/>
+      <x:c r="B81"/>
+      <x:c r="C81"/>
+      <x:c r="D81"/>
+      <x:c r="E81"/>
+      <x:c r="F81"/>
+    </x:row>
+    <x:row r="82">
+      <x:c r="A82"/>
+      <x:c r="B82"/>
+      <x:c r="C82"/>
+      <x:c r="D82"/>
+      <x:c r="E82"/>
+      <x:c r="F82"/>
+    </x:row>
+    <x:row r="83">
+      <x:c r="A83"/>
+      <x:c r="B83"/>
+      <x:c r="C83"/>
+      <x:c r="D83"/>
+      <x:c r="E83"/>
+      <x:c r="F83"/>
+    </x:row>
+    <x:row r="84">
+      <x:c r="A84"/>
+      <x:c r="B84"/>
+      <x:c r="C84"/>
+      <x:c r="D84"/>
+      <x:c r="E84"/>
+      <x:c r="F84"/>
+    </x:row>
+    <x:row r="85">
+      <x:c r="A85"/>
+      <x:c r="B85"/>
+      <x:c r="C85"/>
+      <x:c r="D85"/>
+      <x:c r="E85"/>
+      <x:c r="F85"/>
+    </x:row>
+    <x:row r="86">
+      <x:c r="A86"/>
+      <x:c r="B86"/>
+      <x:c r="C86"/>
+      <x:c r="D86"/>
+      <x:c r="E86"/>
+      <x:c r="F86"/>
+    </x:row>
+    <x:row r="87">
+      <x:c r="A87"/>
+      <x:c r="B87"/>
+      <x:c r="C87"/>
+      <x:c r="D87"/>
+      <x:c r="E87"/>
+      <x:c r="F87"/>
+    </x:row>
+    <x:row r="88">
+      <x:c r="A88"/>
+      <x:c r="B88"/>
+      <x:c r="C88"/>
+      <x:c r="D88"/>
+      <x:c r="E88"/>
+      <x:c r="F88"/>
+    </x:row>
+    <x:row r="89">
+      <x:c r="A89"/>
+      <x:c r="B89"/>
+      <x:c r="C89"/>
+      <x:c r="D89"/>
+      <x:c r="E89"/>
+      <x:c r="F89"/>
+    </x:row>
+    <x:row r="90">
+      <x:c r="A90"/>
+      <x:c r="B90"/>
+      <x:c r="C90"/>
+      <x:c r="D90"/>
+      <x:c r="E90"/>
+      <x:c r="F90"/>
+    </x:row>
+    <x:row r="91">
+      <x:c r="A91"/>
+      <x:c r="B91"/>
+      <x:c r="C91"/>
+      <x:c r="D91"/>
+      <x:c r="E91"/>
+      <x:c r="F91"/>
+    </x:row>
+    <x:row r="92">
+      <x:c r="A92"/>
+      <x:c r="B92"/>
+      <x:c r="C92"/>
+      <x:c r="D92"/>
+      <x:c r="E92"/>
+      <x:c r="F92"/>
+    </x:row>
+    <x:row r="93">
+      <x:c r="A93"/>
+      <x:c r="B93"/>
+      <x:c r="C93"/>
+      <x:c r="D93"/>
+      <x:c r="E93"/>
+      <x:c r="F93"/>
+    </x:row>
+    <x:row r="94">
+      <x:c r="A94"/>
+      <x:c r="B94"/>
+      <x:c r="C94"/>
+      <x:c r="D94"/>
+      <x:c r="E94"/>
+      <x:c r="F94"/>
+    </x:row>
+    <x:row r="95">
+      <x:c r="A95"/>
+      <x:c r="B95"/>
+      <x:c r="C95"/>
+      <x:c r="D95"/>
+      <x:c r="E95"/>
+      <x:c r="F95"/>
+    </x:row>
+    <x:row r="96">
+      <x:c r="A96"/>
+      <x:c r="B96"/>
+      <x:c r="C96"/>
+      <x:c r="D96"/>
+      <x:c r="E96"/>
+      <x:c r="F96"/>
+    </x:row>
+    <x:row r="97">
+      <x:c r="A97"/>
+      <x:c r="B97"/>
+      <x:c r="C97"/>
+      <x:c r="D97"/>
+      <x:c r="E97"/>
+      <x:c r="F97"/>
+    </x:row>
+    <x:row r="98">
+      <x:c r="A98"/>
+      <x:c r="B98"/>
+      <x:c r="C98"/>
+      <x:c r="D98"/>
+      <x:c r="E98"/>
+      <x:c r="F98"/>
+    </x:row>
+    <x:row r="99">
+      <x:c r="A99"/>
+      <x:c r="B99"/>
+      <x:c r="C99"/>
+      <x:c r="D99"/>
+      <x:c r="E99"/>
+      <x:c r="F99"/>
+    </x:row>
+    <x:row r="100">
+      <x:c r="A100"/>
+      <x:c r="B100"/>
+      <x:c r="C100"/>
+      <x:c r="D100"/>
+      <x:c r="E100"/>
+      <x:c r="F100"/>
+    </x:row>
+    <x:row r="101">
+      <x:c r="A101"/>
+      <x:c r="B101"/>
+      <x:c r="C101"/>
+      <x:c r="D101"/>
+      <x:c r="E101"/>
+      <x:c r="F101"/>
+    </x:row>
+    <x:row r="102">
+      <x:c r="A102"/>
+      <x:c r="B102"/>
+      <x:c r="C102"/>
+      <x:c r="D102"/>
+      <x:c r="E102"/>
+      <x:c r="F102"/>
+    </x:row>
+    <x:row r="103">
+      <x:c r="A103"/>
+      <x:c r="B103"/>
+      <x:c r="C103"/>
+      <x:c r="D103"/>
+      <x:c r="E103"/>
+      <x:c r="F103"/>
+    </x:row>
+    <x:row r="104">
+      <x:c r="A104"/>
+      <x:c r="B104"/>
+      <x:c r="C104"/>
+      <x:c r="D104"/>
+      <x:c r="E104"/>
+      <x:c r="F104"/>
+    </x:row>
+    <x:row r="105">
+      <x:c r="A105"/>
+      <x:c r="B105"/>
+      <x:c r="C105"/>
+      <x:c r="D105"/>
+      <x:c r="E105"/>
+      <x:c r="F105"/>
+    </x:row>
+    <x:row r="106">
+      <x:c r="A106"/>
+      <x:c r="B106"/>
+      <x:c r="C106"/>
+      <x:c r="D106"/>
+      <x:c r="E106"/>
+      <x:c r="F106"/>
+    </x:row>
+    <x:row r="107">
+      <x:c r="A107"/>
+      <x:c r="B107"/>
+      <x:c r="C107"/>
+      <x:c r="D107"/>
+      <x:c r="E107"/>
+      <x:c r="F107"/>
+    </x:row>
+    <x:row r="108">
+      <x:c r="A108"/>
+      <x:c r="B108"/>
+      <x:c r="C108"/>
+      <x:c r="D108"/>
+      <x:c r="E108"/>
+      <x:c r="F108"/>
+    </x:row>
+    <x:row r="109">
+      <x:c r="A109"/>
+      <x:c r="B109"/>
+      <x:c r="C109"/>
+      <x:c r="D109"/>
+      <x:c r="E109"/>
+      <x:c r="F109"/>
+    </x:row>
+    <x:row r="110">
+      <x:c r="A110"/>
+      <x:c r="B110"/>
+      <x:c r="C110"/>
+      <x:c r="D110"/>
+      <x:c r="E110"/>
+      <x:c r="F110"/>
+    </x:row>
+    <x:row r="111">
+      <x:c r="A111"/>
+      <x:c r="B111"/>
+      <x:c r="C111"/>
+      <x:c r="D111"/>
+      <x:c r="E111"/>
+      <x:c r="F111"/>
+    </x:row>
+    <x:row r="112">
+      <x:c r="A112"/>
+      <x:c r="B112"/>
+      <x:c r="C112"/>
+      <x:c r="D112"/>
+      <x:c r="E112"/>
+      <x:c r="F112"/>
+    </x:row>
+    <x:row r="113">
+      <x:c r="A113"/>
+      <x:c r="B113"/>
+      <x:c r="C113"/>
+      <x:c r="D113"/>
+      <x:c r="E113"/>
+      <x:c r="F113"/>
+    </x:row>
+    <x:row r="114">
+      <x:c r="A114"/>
+      <x:c r="B114"/>
+      <x:c r="C114"/>
+      <x:c r="D114"/>
+      <x:c r="E114"/>
+      <x:c r="F114"/>
+    </x:row>
+    <x:row r="115">
+      <x:c r="A115"/>
+      <x:c r="B115"/>
+      <x:c r="C115"/>
+      <x:c r="D115"/>
+      <x:c r="E115"/>
+      <x:c r="F115"/>
+    </x:row>
+    <x:row r="116">
+      <x:c r="A116"/>
+      <x:c r="B116"/>
+      <x:c r="C116"/>
+      <x:c r="D116"/>
+      <x:c r="E116"/>
+      <x:c r="F116"/>
+    </x:row>
+    <x:row r="117">
+      <x:c r="A117"/>
+      <x:c r="B117"/>
+      <x:c r="C117"/>
+      <x:c r="D117"/>
+      <x:c r="E117"/>
+      <x:c r="F117"/>
+    </x:row>
+    <x:row r="118">
+      <x:c r="A118"/>
+      <x:c r="B118"/>
+      <x:c r="C118"/>
+      <x:c r="D118"/>
+      <x:c r="E118"/>
+      <x:c r="F118"/>
+    </x:row>
+    <x:row r="119">
+      <x:c r="A119"/>
+      <x:c r="B119"/>
+      <x:c r="C119"/>
+      <x:c r="D119"/>
+      <x:c r="E119"/>
+      <x:c r="F119"/>
+    </x:row>
+    <x:row r="120">
+      <x:c r="A120"/>
+      <x:c r="B120"/>
+      <x:c r="C120"/>
+      <x:c r="D120"/>
+      <x:c r="E120"/>
+      <x:c r="F120"/>
+    </x:row>
+    <x:row r="121">
+      <x:c r="A121"/>
+      <x:c r="B121"/>
+      <x:c r="C121"/>
+      <x:c r="D121"/>
+      <x:c r="E121"/>
+      <x:c r="F121"/>
+    </x:row>
+    <x:row r="122">
+      <x:c r="A122"/>
+      <x:c r="B122"/>
+      <x:c r="C122"/>
+      <x:c r="D122"/>
+      <x:c r="E122"/>
+      <x:c r="F122"/>
+    </x:row>
+    <x:row r="123">
+      <x:c r="A123"/>
+      <x:c r="B123"/>
+      <x:c r="C123"/>
+      <x:c r="D123"/>
+      <x:c r="E123"/>
+      <x:c r="F123"/>
+    </x:row>
+    <x:row r="124">
+      <x:c r="A124"/>
+      <x:c r="B124"/>
+      <x:c r="C124"/>
+      <x:c r="D124"/>
+      <x:c r="E124"/>
+      <x:c r="F124"/>
+    </x:row>
+    <x:row r="125">
+      <x:c r="A125"/>
+      <x:c r="B125"/>
+      <x:c r="C125"/>
+      <x:c r="D125"/>
+      <x:c r="E125"/>
+      <x:c r="F125"/>
+    </x:row>
+    <x:row r="126">
+      <x:c r="A126"/>
+      <x:c r="B126"/>
+      <x:c r="C126"/>
+      <x:c r="D126"/>
+      <x:c r="E126"/>
+      <x:c r="F126"/>
+    </x:row>
+    <x:row r="127">
+      <x:c r="A127"/>
+      <x:c r="B127"/>
+      <x:c r="C127"/>
+      <x:c r="D127"/>
+      <x:c r="E127"/>
+      <x:c r="F127"/>
+    </x:row>
+    <x:row r="128">
+      <x:c r="A128"/>
+      <x:c r="B128"/>
+      <x:c r="C128"/>
+      <x:c r="D128"/>
+      <x:c r="E128"/>
+      <x:c r="F128"/>
+    </x:row>
+    <x:row r="129">
+      <x:c r="A129"/>
+      <x:c r="B129"/>
+      <x:c r="C129"/>
+      <x:c r="D129"/>
+      <x:c r="E129"/>
+      <x:c r="F129"/>
+    </x:row>
+    <x:row r="130">
+      <x:c r="A130"/>
+      <x:c r="B130"/>
+      <x:c r="C130"/>
+      <x:c r="D130"/>
+      <x:c r="E130"/>
+      <x:c r="F130"/>
+    </x:row>
+    <x:row r="131">
+      <x:c r="A131"/>
+      <x:c r="B131"/>
+      <x:c r="C131"/>
+      <x:c r="D131"/>
+      <x:c r="E131"/>
+      <x:c r="F131"/>
+    </x:row>
+    <x:row r="132">
+      <x:c r="A132"/>
+      <x:c r="B132"/>
+      <x:c r="C132"/>
+      <x:c r="D132"/>
+      <x:c r="E132"/>
+      <x:c r="F132"/>
+    </x:row>
+    <x:row r="133">
+      <x:c r="A133"/>
+      <x:c r="B133"/>
+      <x:c r="C133"/>
+      <x:c r="D133"/>
+      <x:c r="E133"/>
+      <x:c r="F133"/>
+    </x:row>
+    <x:row r="134">
+      <x:c r="A134"/>
+      <x:c r="B134"/>
+      <x:c r="C134"/>
+      <x:c r="D134"/>
+      <x:c r="E134"/>
+      <x:c r="F134"/>
+    </x:row>
+    <x:row r="135">
+      <x:c r="A135"/>
+      <x:c r="B135"/>
+      <x:c r="C135"/>
+      <x:c r="D135"/>
+      <x:c r="E135"/>
+      <x:c r="F135"/>
+    </x:row>
+    <x:row r="136">
+      <x:c r="A136"/>
+      <x:c r="B136"/>
+      <x:c r="C136"/>
+      <x:c r="D136"/>
+      <x:c r="E136"/>
+      <x:c r="F136"/>
+    </x:row>
+    <x:row r="137">
+      <x:c r="A137"/>
+      <x:c r="B137"/>
+      <x:c r="C137"/>
+      <x:c r="D137"/>
+      <x:c r="E137"/>
+      <x:c r="F137"/>
+    </x:row>
+    <x:row r="138">
+      <x:c r="A138"/>
+      <x:c r="B138"/>
+      <x:c r="C138"/>
+      <x:c r="D138"/>
+      <x:c r="E138"/>
+      <x:c r="F138"/>
+    </x:row>
+    <x:row r="139">
+      <x:c r="A139"/>
+      <x:c r="B139"/>
+      <x:c r="C139"/>
+      <x:c r="D139"/>
+      <x:c r="E139"/>
+      <x:c r="F139"/>
+    </x:row>
+    <x:row r="140">
+      <x:c r="A140"/>
+      <x:c r="B140"/>
+      <x:c r="C140"/>
+      <x:c r="D140"/>
+      <x:c r="E140"/>
+      <x:c r="F140"/>
+    </x:row>
+    <x:row r="141">
+      <x:c r="A141"/>
+      <x:c r="B141"/>
+      <x:c r="C141"/>
+      <x:c r="D141"/>
+      <x:c r="E141"/>
+      <x:c r="F141"/>
+    </x:row>
+    <x:row r="142">
+      <x:c r="A142"/>
+      <x:c r="B142"/>
+      <x:c r="C142"/>
+      <x:c r="D142"/>
+      <x:c r="E142"/>
+      <x:c r="F142"/>
+    </x:row>
+    <x:row r="143">
+      <x:c r="A143"/>
+      <x:c r="B143"/>
+      <x:c r="C143"/>
+      <x:c r="D143"/>
+      <x:c r="E143"/>
+      <x:c r="F143"/>
+    </x:row>
+    <x:row r="144">
+      <x:c r="A144"/>
+      <x:c r="B144"/>
+      <x:c r="C144"/>
+      <x:c r="D144"/>
+      <x:c r="E144"/>
+      <x:c r="F144"/>
+    </x:row>
+    <x:row r="145">
+      <x:c r="A145"/>
+      <x:c r="B145"/>
+      <x:c r="C145"/>
+      <x:c r="D145"/>
+      <x:c r="E145"/>
+      <x:c r="F145"/>
+    </x:row>
+    <x:row r="146">
+      <x:c r="A146"/>
+      <x:c r="B146"/>
+      <x:c r="C146"/>
+      <x:c r="D146"/>
+      <x:c r="E146"/>
+      <x:c r="F146"/>
+    </x:row>
+    <x:row r="147">
+      <x:c r="A147"/>
+      <x:c r="B147"/>
+      <x:c r="C147"/>
+      <x:c r="D147"/>
+      <x:c r="E147"/>
+      <x:c r="F147"/>
+    </x:row>
+    <x:row r="148">
+      <x:c r="A148"/>
+      <x:c r="B148"/>
+      <x:c r="C148"/>
+      <x:c r="D148"/>
+      <x:c r="E148"/>
+      <x:c r="F148"/>
+    </x:row>
+    <x:row r="149">
+      <x:c r="A149"/>
+      <x:c r="B149"/>
+      <x:c r="C149"/>
+      <x:c r="D149"/>
+      <x:c r="E149"/>
+      <x:c r="F149"/>
+    </x:row>
+    <x:row r="150">
+      <x:c r="A150"/>
+      <x:c r="B150"/>
+      <x:c r="C150"/>
+      <x:c r="D150"/>
+      <x:c r="E150"/>
+      <x:c r="F150"/>
+    </x:row>
+    <x:row r="151">
+      <x:c r="A151"/>
+      <x:c r="B151"/>
+      <x:c r="C151"/>
+      <x:c r="D151"/>
+      <x:c r="E151"/>
+      <x:c r="F151"/>
+    </x:row>
+    <x:row r="152">
+      <x:c r="A152"/>
+      <x:c r="B152"/>
+      <x:c r="C152"/>
+      <x:c r="D152"/>
+      <x:c r="E152"/>
+      <x:c r="F152"/>
+    </x:row>
+    <x:row r="153">
+      <x:c r="A153"/>
+      <x:c r="B153"/>
+      <x:c r="C153"/>
+      <x:c r="D153"/>
+      <x:c r="E153"/>
+      <x:c r="F153"/>
+    </x:row>
+    <x:row r="154">
+      <x:c r="A154"/>
+      <x:c r="B154"/>
+      <x:c r="C154"/>
+      <x:c r="D154"/>
+      <x:c r="E154"/>
+      <x:c r="F154"/>
+    </x:row>
+    <x:row r="155">
+      <x:c r="A155"/>
+      <x:c r="B155"/>
+      <x:c r="C155"/>
+      <x:c r="D155"/>
+      <x:c r="E155"/>
+      <x:c r="F155"/>
+    </x:row>
+    <x:row r="156">
+      <x:c r="A156"/>
+      <x:c r="B156"/>
+      <x:c r="C156"/>
+      <x:c r="D156"/>
+      <x:c r="E156"/>
+      <x:c r="F156"/>
+    </x:row>
+    <x:row r="157">
+      <x:c r="A157"/>
+      <x:c r="B157"/>
+      <x:c r="C157"/>
+      <x:c r="D157"/>
+      <x:c r="E157"/>
+      <x:c r="F157"/>
+    </x:row>
+    <x:row r="158">
+      <x:c r="A158"/>
+      <x:c r="B158"/>
+      <x:c r="C158"/>
+      <x:c r="D158"/>
+      <x:c r="E158"/>
+      <x:c r="F158"/>
+    </x:row>
+    <x:row r="159">
+      <x:c r="A159"/>
+      <x:c r="B159"/>
+      <x:c r="C159"/>
+      <x:c r="D159"/>
+      <x:c r="E159"/>
+      <x:c r="F159"/>
+    </x:row>
+    <x:row r="160">
+      <x:c r="A160"/>
+      <x:c r="B160"/>
+      <x:c r="C160"/>
+      <x:c r="D160"/>
+      <x:c r="E160"/>
+      <x:c r="F160"/>
+    </x:row>
+    <x:row r="161">
+      <x:c r="A161"/>
+      <x:c r="B161"/>
+      <x:c r="C161"/>
+      <x:c r="D161"/>
+      <x:c r="E161"/>
+      <x:c r="F161"/>
+    </x:row>
+    <x:row r="162">
+      <x:c r="A162"/>
+      <x:c r="B162"/>
+      <x:c r="C162"/>
+      <x:c r="D162"/>
+      <x:c r="E162"/>
+      <x:c r="F162"/>
+    </x:row>
+    <x:row r="163">
+      <x:c r="A163"/>
+      <x:c r="B163"/>
+      <x:c r="C163"/>
+      <x:c r="D163"/>
+      <x:c r="E163"/>
+      <x:c r="F163"/>
+    </x:row>
+    <x:row r="164">
+      <x:c r="A164"/>
+      <x:c r="B164"/>
+      <x:c r="C164"/>
+      <x:c r="D164"/>
+      <x:c r="E164"/>
+      <x:c r="F164"/>
+    </x:row>
+    <x:row r="165">
+      <x:c r="A165"/>
+      <x:c r="B165"/>
+      <x:c r="C165"/>
+      <x:c r="D165"/>
+      <x:c r="E165"/>
+      <x:c r="F165"/>
+    </x:row>
+    <x:row r="166">
+      <x:c r="A166"/>
+      <x:c r="B166"/>
+      <x:c r="C166"/>
+      <x:c r="D166"/>
+      <x:c r="E166"/>
+      <x:c r="F166"/>
+    </x:row>
+    <x:row r="167">
+      <x:c r="A167"/>
+      <x:c r="B167"/>
+      <x:c r="C167"/>
+      <x:c r="D167"/>
+      <x:c r="E167"/>
+      <x:c r="F167"/>
+    </x:row>
+    <x:row r="168">
+      <x:c r="A168"/>
+      <x:c r="B168"/>
+      <x:c r="C168"/>
+      <x:c r="D168"/>
+      <x:c r="E168"/>
+      <x:c r="F168"/>
+    </x:row>
+    <x:row r="169">
+      <x:c r="A169"/>
+      <x:c r="B169"/>
+      <x:c r="C169"/>
+      <x:c r="D169"/>
+      <x:c r="E169"/>
+      <x:c r="F169"/>
+    </x:row>
+    <x:row r="170">
+      <x:c r="A170"/>
+      <x:c r="B170"/>
+      <x:c r="C170"/>
+      <x:c r="D170"/>
+      <x:c r="E170"/>
+      <x:c r="F170"/>
+    </x:row>
+    <x:row r="171">
+      <x:c r="A171"/>
+      <x:c r="B171"/>
+      <x:c r="C171"/>
+      <x:c r="D171"/>
+      <x:c r="E171"/>
+      <x:c r="F171"/>
+    </x:row>
+    <x:row r="172">
+      <x:c r="A172"/>
+      <x:c r="B172"/>
+      <x:c r="C172"/>
+      <x:c r="D172"/>
+      <x:c r="E172"/>
+      <x:c r="F172"/>
+    </x:row>
+    <x:row r="173">
+      <x:c r="A173"/>
+      <x:c r="B173"/>
+      <x:c r="C173"/>
+      <x:c r="D173"/>
+      <x:c r="E173"/>
+      <x:c r="F173"/>
+    </x:row>
+    <x:row r="174">
+      <x:c r="A174"/>
+      <x:c r="B174"/>
+      <x:c r="C174"/>
+      <x:c r="D174"/>
+      <x:c r="E174"/>
+      <x:c r="F174"/>
+    </x:row>
+    <x:row r="175">
+      <x:c r="A175"/>
+      <x:c r="B175"/>
+      <x:c r="C175"/>
+      <x:c r="D175"/>
+      <x:c r="E175"/>
+      <x:c r="F175"/>
+    </x:row>
+    <x:row r="176">
+      <x:c r="A176"/>
+      <x:c r="B176"/>
+      <x:c r="C176"/>
+      <x:c r="D176"/>
+      <x:c r="E176"/>
+      <x:c r="F176"/>
+    </x:row>
+    <x:row r="177">
+      <x:c r="A177"/>
+      <x:c r="B177"/>
+      <x:c r="C177"/>
+      <x:c r="D177"/>
+      <x:c r="E177"/>
+      <x:c r="F177"/>
+    </x:row>
+    <x:row r="178">
+      <x:c r="A178"/>
+      <x:c r="B178"/>
+      <x:c r="C178"/>
+      <x:c r="D178"/>
+      <x:c r="E178"/>
+      <x:c r="F178"/>
+    </x:row>
+    <x:row r="179">
+      <x:c r="A179"/>
+      <x:c r="B179"/>
+      <x:c r="C179"/>
+      <x:c r="D179"/>
+      <x:c r="E179"/>
+      <x:c r="F179"/>
+    </x:row>
+    <x:row r="180">
+      <x:c r="A180"/>
+      <x:c r="B180"/>
+      <x:c r="C180"/>
+      <x:c r="D180"/>
+      <x:c r="E180"/>
+      <x:c r="F180"/>
+    </x:row>
+    <x:row r="181">
+      <x:c r="A181"/>
+      <x:c r="B181"/>
+      <x:c r="C181"/>
+      <x:c r="D181"/>
+      <x:c r="E181"/>
+      <x:c r="F181"/>
+    </x:row>
+    <x:row r="182">
+      <x:c r="A182"/>
+      <x:c r="B182"/>
+      <x:c r="C182"/>
+      <x:c r="D182"/>
+      <x:c r="E182"/>
+      <x:c r="F182"/>
+    </x:row>
+    <x:row r="183">
+      <x:c r="A183"/>
+      <x:c r="B183"/>
+      <x:c r="C183"/>
+      <x:c r="D183"/>
+      <x:c r="E183"/>
+      <x:c r="F183"/>
+    </x:row>
+    <x:row r="184">
+      <x:c r="A184"/>
+      <x:c r="B184"/>
+      <x:c r="C184"/>
+      <x:c r="D184"/>
+      <x:c r="E184"/>
+      <x:c r="F184"/>
+    </x:row>
+    <x:row r="185">
+      <x:c r="A185"/>
+      <x:c r="B185"/>
+      <x:c r="C185"/>
+      <x:c r="D185"/>
+      <x:c r="E185"/>
+      <x:c r="F185"/>
+    </x:row>
+    <x:row r="186">
+      <x:c r="A186"/>
+      <x:c r="B186"/>
+      <x:c r="C186"/>
+      <x:c r="D186"/>
+      <x:c r="E186"/>
+      <x:c r="F186"/>
+    </x:row>
+    <x:row r="187">
+      <x:c r="A187"/>
+      <x:c r="B187"/>
+      <x:c r="C187"/>
+      <x:c r="D187"/>
+      <x:c r="E187"/>
+      <x:c r="F187"/>
+    </x:row>
+    <x:row r="188">
+      <x:c r="A188"/>
+      <x:c r="B188"/>
+      <x:c r="C188"/>
+      <x:c r="D188"/>
+      <x:c r="E188"/>
+      <x:c r="F188"/>
+    </x:row>
+    <x:row r="189">
+      <x:c r="A189"/>
+      <x:c r="B189"/>
+      <x:c r="C189"/>
+      <x:c r="D189"/>
+      <x:c r="E189"/>
+      <x:c r="F189"/>
+    </x:row>
+    <x:row r="190">
+      <x:c r="A190"/>
+      <x:c r="B190"/>
+      <x:c r="C190"/>
+      <x:c r="D190"/>
+      <x:c r="E190"/>
+      <x:c r="F190"/>
+    </x:row>
+    <x:row r="191">
+      <x:c r="A191"/>
+      <x:c r="B191"/>
+      <x:c r="C191"/>
+      <x:c r="D191"/>
+      <x:c r="E191"/>
+      <x:c r="F191"/>
+    </x:row>
+    <x:row r="192">
+      <x:c r="A192"/>
+      <x:c r="B192"/>
+      <x:c r="C192"/>
+      <x:c r="D192"/>
+      <x:c r="E192"/>
+      <x:c r="F192"/>
+    </x:row>
+    <x:row r="193">
+      <x:c r="A193"/>
+      <x:c r="B193"/>
+      <x:c r="C193"/>
+      <x:c r="D193"/>
+      <x:c r="E193"/>
+      <x:c r="F193"/>
+    </x:row>
+    <x:row r="194">
+      <x:c r="A194"/>
+      <x:c r="B194"/>
+      <x:c r="C194"/>
+      <x:c r="D194"/>
+      <x:c r="E194"/>
+      <x:c r="F194"/>
+    </x:row>
+    <x:row r="195">
+      <x:c r="A195"/>
+      <x:c r="B195"/>
+      <x:c r="C195"/>
+      <x:c r="D195"/>
+      <x:c r="E195"/>
+      <x:c r="F195"/>
+    </x:row>
+    <x:row r="196">
+      <x:c r="A196"/>
+      <x:c r="B196"/>
+      <x:c r="C196"/>
+      <x:c r="D196"/>
+      <x:c r="E196"/>
+      <x:c r="F196"/>
+    </x:row>
+    <x:row r="197">
+      <x:c r="A197"/>
+      <x:c r="B197"/>
+      <x:c r="C197"/>
+      <x:c r="D197"/>
+      <x:c r="E197"/>
+      <x:c r="F197"/>
+    </x:row>
+    <x:row r="198">
+      <x:c r="A198"/>
+      <x:c r="B198"/>
+      <x:c r="C198"/>
+      <x:c r="D198"/>
+      <x:c r="E198"/>
+      <x:c r="F198"/>
+    </x:row>
+    <x:row r="199">
+      <x:c r="A199"/>
+      <x:c r="B199"/>
+      <x:c r="C199"/>
+      <x:c r="D199"/>
+      <x:c r="E199"/>
+      <x:c r="F199"/>
+    </x:row>
+    <x:row r="200">
+      <x:c r="A200"/>
+      <x:c r="B200"/>
+      <x:c r="C200"/>
+      <x:c r="D200"/>
+      <x:c r="E200"/>
+      <x:c r="F200"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/GourmetProject/GameConfig/Datas/term.xlsx
+++ b/GourmetProject/GameConfig/Datas/term.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="term" sheetId="1" r:id="Rc6ab822897d54a10"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="term" sheetId="1" r:id="Re5613928751d48ac"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1119,8 +1119,8 @@
         <x:v>酸</x:v>
       </x:c>
       <x:c r="D9" s="2" t="str">
-        <x:v>结算开始时，若仍在食谱中
-场上食物倍率 +0.5</x:v>
+        <x:v>[context]结算开始[/context]时，若仍在食谱中
+场上食物[strong]倍率[/strong] [multadd]+0.5[/multadd]</x:v>
       </x:c>
       <x:c r="E9"/>
       <x:c r="F9"/>
@@ -1134,7 +1134,7 @@
         <x:v>咸</x:v>
       </x:c>
       <x:c r="D10" s="2" t="str">
-        <x:v>有 20% 概率额外结算 1 次</x:v>
+        <x:v>有 20% 概率[benefit]额外结算[/benefit] 1 次</x:v>
       </x:c>
       <x:c r="E10"/>
       <x:c r="F10"/>
@@ -1148,8 +1148,8 @@
         <x:v>欢乐蛋糕</x:v>
       </x:c>
       <x:c r="D11" s="2" t="str">
-        <x:v>根据蛋糕层数
-对场上所有蛋糕食物增益</x:v>
+        <x:v>根据[term]蛋糕[/term]层数
+对场上所有[term]蛋糕[/term]食物增益</x:v>
       </x:c>
       <x:c r="E11"/>
       <x:c r="F11"/>
@@ -1163,7 +1163,7 @@
         <x:v>樱桃木</x:v>
       </x:c>
       <x:c r="D12" s="3" t="str">
-        <x:v>分数 +60</x:v>
+        <x:v>[strong]分数[/strong] [score]+60[/score]</x:v>
       </x:c>
       <x:c r="E12"/>
       <x:c r="F12"/>
@@ -1177,7 +1177,7 @@
         <x:v>胡桃木</x:v>
       </x:c>
       <x:c r="D13" s="3" t="str">
-        <x:v>分数永久 +15</x:v>
+        <x:v>[strong]分数[/strong]永久 [score]+15[/score]</x:v>
       </x:c>
       <x:c r="E13"/>
       <x:c r="F13"/>
@@ -1191,7 +1191,7 @@
         <x:v>大理石</x:v>
       </x:c>
       <x:c r="D14" s="3" t="str">
-        <x:v>倍率 +2</x:v>
+        <x:v>[strong]倍率[/strong] [multadd]+2[/multadd]</x:v>
       </x:c>
       <x:c r="E14"/>
       <x:c r="F14"/>
@@ -1205,7 +1205,7 @@
         <x:v>黑曜石</x:v>
       </x:c>
       <x:c r="D15" s="3" t="str">
-        <x:v>倍率 ×1.5</x:v>
+        <x:v>[strong]倍率[/strong] [multmul]×1.5[/multmul]</x:v>
       </x:c>
       <x:c r="E15"/>
       <x:c r="F15"/>
@@ -1220,7 +1220,7 @@
       </x:c>
       <x:c r="D16" s="4" t="str">
         <x:v>每占 1 格翡翠
-倍率 +0.8</x:v>
+[strong]倍率[/strong] [multadd]+0.8[/multadd]</x:v>
       </x:c>
       <x:c r="E16"/>
       <x:c r="F16"/>
@@ -1235,7 +1235,7 @@
       </x:c>
       <x:c r="D17" s="4" t="str">
         <x:v>占据 2 格金餐桌时
-+15 金币</x:v>
+[gold]+15 金币[/gold]</x:v>
       </x:c>
       <x:c r="E17"/>
       <x:c r="F17"/>
@@ -1250,7 +1250,7 @@
       </x:c>
       <x:c r="D18" s="4" t="str">
         <x:v>占据 2 格银餐桌时
-1/2 概率获得消耗品</x:v>
+1/2 概率获得[term]消耗品[/term]</x:v>
       </x:c>
       <x:c r="E18"/>
       <x:c r="F18"/>

--- a/GourmetProject/GameConfig/Datas/term.xlsx
+++ b/GourmetProject/GameConfig/Datas/term.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="term" sheetId="1" r:id="Rd847f4e211354d6e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="term" sheetId="1" r:id="R3766bfa3df5d4d14"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1139,7 +1139,7 @@
       <x:c r="D4" s="4" t="str">
         <x:v>使随机食物获得此技能
 并结算其获得的
-所有甜蜜传递技能</x:v>
+[context]所有[/context]甜蜜传递技能</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
